--- a/extract.xlsx
+++ b/extract.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trial\auto-rep-hack\Automatic-Replenish-Extractor\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19EEFF7C-2B99-4460-B3FD-EF9AE2DD96B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="7815"/>
+    <workbookView xWindow="15" yWindow="0" windowWidth="10080" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="(2025-08-19 11-29) 21-141 Bayan" sheetId="1" r:id="rId1"/>
@@ -935,14 +941,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="42" formatCode="_-&quot;₱&quot;* #,##0_-;\-&quot;₱&quot;* #,##0_-;_-&quot;₱&quot;* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;₱&quot;* #,##0.00_-;\-&quot;₱&quot;* #,##0.00_-;_-&quot;₱&quot;* &quot;-&quot;??_-;_-@_-"/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -960,342 +960,19 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Aptos Display"/>
-      <charset val="134"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C5700"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1303,246 +980,33 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.399975585192419"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1820,20 +1284,20 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B300"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" spans="1:2">
+    <row r="1" spans="1:2" ht="15.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1841,7 +1305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" ht="15">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -1849,7 +1313,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" ht="15">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -1857,7 +1321,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" ht="15">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
@@ -1865,7 +1329,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" ht="15">
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
@@ -1873,7 +1337,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" ht="15">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
@@ -1881,7 +1345,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" ht="15">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
@@ -1889,7 +1353,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" ht="15">
       <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
@@ -1897,7 +1361,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" ht="15">
       <c r="A9" s="2" t="s">
         <v>9</v>
       </c>
@@ -1905,7 +1369,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" ht="15">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -1913,7 +1377,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" ht="15">
       <c r="A11" s="2" t="s">
         <v>11</v>
       </c>
@@ -1921,7 +1385,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" ht="15">
       <c r="A12" s="2" t="s">
         <v>12</v>
       </c>
@@ -1929,7 +1393,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" ht="15">
       <c r="A13" s="2" t="s">
         <v>13</v>
       </c>
@@ -1937,7 +1401,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" ht="15">
       <c r="A14" s="2" t="s">
         <v>14</v>
       </c>
@@ -1945,7 +1409,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" ht="15">
       <c r="A15" s="2" t="s">
         <v>15</v>
       </c>
@@ -1953,7 +1417,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" ht="15">
       <c r="A16" s="2" t="s">
         <v>16</v>
       </c>
@@ -1961,7 +1425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" ht="15">
       <c r="A17" s="2" t="s">
         <v>17</v>
       </c>
@@ -1969,7 +1433,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" ht="15">
       <c r="A18" s="2" t="s">
         <v>18</v>
       </c>
@@ -1977,7 +1441,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" ht="15">
       <c r="A19" s="2" t="s">
         <v>19</v>
       </c>
@@ -1985,7 +1449,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" ht="15">
       <c r="A20" s="2" t="s">
         <v>20</v>
       </c>
@@ -1993,7 +1457,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" ht="15">
       <c r="A21" s="2" t="s">
         <v>21</v>
       </c>
@@ -2001,7 +1465,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" ht="15">
       <c r="A22" s="2" t="s">
         <v>22</v>
       </c>
@@ -2009,7 +1473,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" ht="15">
       <c r="A23" s="2" t="s">
         <v>23</v>
       </c>
@@ -2017,7 +1481,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" ht="15">
       <c r="A24" s="2" t="s">
         <v>24</v>
       </c>
@@ -2025,7 +1489,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" ht="15">
       <c r="A25" s="2" t="s">
         <v>25</v>
       </c>
@@ -2033,7 +1497,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" ht="15">
       <c r="A26" s="2" t="s">
         <v>26</v>
       </c>
@@ -2041,7 +1505,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" ht="15">
       <c r="A27" s="2" t="s">
         <v>27</v>
       </c>
@@ -2049,7 +1513,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" ht="15">
       <c r="A28" s="2" t="s">
         <v>28</v>
       </c>
@@ -2057,7 +1521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" ht="15">
       <c r="A29" s="2" t="s">
         <v>29</v>
       </c>
@@ -2065,7 +1529,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" ht="15">
       <c r="A30" s="2" t="s">
         <v>30</v>
       </c>
@@ -2073,7 +1537,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" ht="15">
       <c r="A31" s="2" t="s">
         <v>31</v>
       </c>
@@ -2081,7 +1545,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" ht="15">
       <c r="A32" s="2" t="s">
         <v>32</v>
       </c>
@@ -2089,7 +1553,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" ht="15">
       <c r="A33" s="2" t="s">
         <v>33</v>
       </c>
@@ -2097,7 +1561,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" ht="15">
       <c r="A34" s="2" t="s">
         <v>34</v>
       </c>
@@ -2105,7 +1569,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" ht="15">
       <c r="A35" s="2" t="s">
         <v>35</v>
       </c>
@@ -2113,7 +1577,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" ht="15">
       <c r="A36" s="2" t="s">
         <v>36</v>
       </c>
@@ -2121,7 +1585,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" ht="15">
       <c r="A37" s="2" t="s">
         <v>37</v>
       </c>
@@ -2129,7 +1593,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" ht="15">
       <c r="A38" s="2" t="s">
         <v>38</v>
       </c>
@@ -2137,7 +1601,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" ht="15">
       <c r="A39" s="2" t="s">
         <v>39</v>
       </c>
@@ -2145,7 +1609,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" ht="15">
       <c r="A40" s="2" t="s">
         <v>40</v>
       </c>
@@ -2153,7 +1617,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" ht="15">
       <c r="A41" s="2" t="s">
         <v>41</v>
       </c>
@@ -2161,7 +1625,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" ht="15">
       <c r="A42" s="2" t="s">
         <v>42</v>
       </c>
@@ -2169,7 +1633,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" ht="15">
       <c r="A43" s="2" t="s">
         <v>43</v>
       </c>
@@ -2177,7 +1641,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" ht="15">
       <c r="A44" s="2" t="s">
         <v>44</v>
       </c>
@@ -2185,7 +1649,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" ht="15">
       <c r="A45" s="2" t="s">
         <v>45</v>
       </c>
@@ -2193,7 +1657,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" ht="15">
       <c r="A46" s="2" t="s">
         <v>46</v>
       </c>
@@ -2201,7 +1665,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" ht="15">
       <c r="A47" s="2" t="s">
         <v>47</v>
       </c>
@@ -2209,7 +1673,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" ht="15">
       <c r="A48" s="2" t="s">
         <v>48</v>
       </c>
@@ -2217,7 +1681,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" ht="15">
       <c r="A49" s="2" t="s">
         <v>49</v>
       </c>
@@ -2225,7 +1689,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" ht="15">
       <c r="A50" s="2" t="s">
         <v>50</v>
       </c>
@@ -2233,7 +1697,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" ht="15">
       <c r="A51" s="2" t="s">
         <v>51</v>
       </c>
@@ -2241,7 +1705,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" ht="15">
       <c r="A52" s="2" t="s">
         <v>52</v>
       </c>
@@ -2249,7 +1713,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" ht="15">
       <c r="A53" s="2" t="s">
         <v>53</v>
       </c>
@@ -2257,13 +1721,13 @@
         <v>195</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" ht="15">
       <c r="A54" s="2" t="s">
         <v>54</v>
       </c>
       <c r="B54" s="3"/>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" ht="15">
       <c r="A55" s="2" t="s">
         <v>55</v>
       </c>
@@ -2271,7 +1735,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" ht="15">
       <c r="A56" s="2" t="s">
         <v>56</v>
       </c>
@@ -2279,7 +1743,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" ht="15">
       <c r="A57" s="2" t="s">
         <v>57</v>
       </c>
@@ -2287,7 +1751,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" ht="15">
       <c r="A58" s="2" t="s">
         <v>58</v>
       </c>
@@ -2295,7 +1759,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" ht="15">
       <c r="A59" s="2" t="s">
         <v>59</v>
       </c>
@@ -2303,7 +1767,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" ht="15">
       <c r="A60" s="2" t="s">
         <v>60</v>
       </c>
@@ -2311,7 +1775,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:2" ht="15">
       <c r="A61" s="2" t="s">
         <v>61</v>
       </c>
@@ -2319,7 +1783,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:2" ht="15">
       <c r="A62" s="2" t="s">
         <v>62</v>
       </c>
@@ -2327,7 +1791,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="1:2" ht="15">
       <c r="A63" s="2" t="s">
         <v>63</v>
       </c>
@@ -2335,7 +1799,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="1:2" ht="15">
       <c r="A64" s="2" t="s">
         <v>64</v>
       </c>
@@ -2343,7 +1807,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
+    <row r="65" spans="1:2" ht="15">
       <c r="A65" s="2" t="s">
         <v>65</v>
       </c>
@@ -2351,7 +1815,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
+    <row r="66" spans="1:2" ht="15">
       <c r="A66" s="2" t="s">
         <v>66</v>
       </c>
@@ -2359,7 +1823,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
+    <row r="67" spans="1:2" ht="15">
       <c r="A67" s="2" t="s">
         <v>67</v>
       </c>
@@ -2367,7 +1831,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
+    <row r="68" spans="1:2" ht="15">
       <c r="A68" s="2" t="s">
         <v>68</v>
       </c>
@@ -2375,7 +1839,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
+    <row r="69" spans="1:2" ht="15">
       <c r="A69" s="2" t="s">
         <v>69</v>
       </c>
@@ -2383,7 +1847,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
+    <row r="70" spans="1:2" ht="15">
       <c r="A70" s="2" t="s">
         <v>70</v>
       </c>
@@ -2391,7 +1855,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
+    <row r="71" spans="1:2" ht="15">
       <c r="A71" s="2" t="s">
         <v>71</v>
       </c>
@@ -2399,7 +1863,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
+    <row r="72" spans="1:2" ht="15">
       <c r="A72" s="2" t="s">
         <v>72</v>
       </c>
@@ -2407,7 +1871,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
+    <row r="73" spans="1:2" ht="15">
       <c r="A73" s="2" t="s">
         <v>73</v>
       </c>
@@ -2415,7 +1879,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="74" spans="1:2">
+    <row r="74" spans="1:2" ht="15">
       <c r="A74" s="2" t="s">
         <v>74</v>
       </c>
@@ -2423,7 +1887,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:2">
+    <row r="75" spans="1:2" ht="15">
       <c r="A75" s="2" t="s">
         <v>75</v>
       </c>
@@ -2431,7 +1895,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:2">
+    <row r="76" spans="1:2" ht="15">
       <c r="A76" s="2" t="s">
         <v>76</v>
       </c>
@@ -2439,7 +1903,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:2">
+    <row r="77" spans="1:2" ht="15">
       <c r="A77" s="2" t="s">
         <v>77</v>
       </c>
@@ -2447,7 +1911,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:2">
+    <row r="78" spans="1:2" ht="15">
       <c r="A78" s="2" t="s">
         <v>78</v>
       </c>
@@ -2455,7 +1919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:2">
+    <row r="79" spans="1:2" ht="15">
       <c r="A79" s="2" t="s">
         <v>79</v>
       </c>
@@ -2463,7 +1927,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:2">
+    <row r="80" spans="1:2" ht="15">
       <c r="A80" s="2" t="s">
         <v>80</v>
       </c>
@@ -2471,7 +1935,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
+    <row r="81" spans="1:2" ht="15">
       <c r="A81" s="2" t="s">
         <v>81</v>
       </c>
@@ -2479,7 +1943,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
+    <row r="82" spans="1:2" ht="15">
       <c r="A82" s="2" t="s">
         <v>82</v>
       </c>
@@ -2487,7 +1951,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="83" spans="1:2">
+    <row r="83" spans="1:2" ht="15">
       <c r="A83" s="2" t="s">
         <v>83</v>
       </c>
@@ -2495,7 +1959,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
+    <row r="84" spans="1:2" ht="15">
       <c r="A84" s="2" t="s">
         <v>84</v>
       </c>
@@ -2503,7 +1967,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
+    <row r="85" spans="1:2" ht="15">
       <c r="A85" s="2" t="s">
         <v>85</v>
       </c>
@@ -2511,7 +1975,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
+    <row r="86" spans="1:2" ht="15">
       <c r="A86" s="2" t="s">
         <v>86</v>
       </c>
@@ -2519,7 +1983,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="87" spans="1:2">
+    <row r="87" spans="1:2" ht="15">
       <c r="A87" s="2" t="s">
         <v>87</v>
       </c>
@@ -2527,7 +1991,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
+    <row r="88" spans="1:2" ht="15">
       <c r="A88" s="2" t="s">
         <v>88</v>
       </c>
@@ -2535,7 +1999,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="89" spans="1:2">
+    <row r="89" spans="1:2" ht="15">
       <c r="A89" s="2" t="s">
         <v>89</v>
       </c>
@@ -2543,7 +2007,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="90" spans="1:2">
+    <row r="90" spans="1:2" ht="15">
       <c r="A90" s="2" t="s">
         <v>90</v>
       </c>
@@ -2551,7 +2015,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="91" spans="1:2">
+    <row r="91" spans="1:2" ht="15">
       <c r="A91" s="2" t="s">
         <v>91</v>
       </c>
@@ -2559,13 +2023,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="1:2">
+    <row r="92" spans="1:2" ht="15">
       <c r="A92" s="2" t="s">
         <v>92</v>
       </c>
       <c r="B92" s="3"/>
     </row>
-    <row r="93" spans="1:2">
+    <row r="93" spans="1:2" ht="15">
       <c r="A93" s="2" t="s">
         <v>93</v>
       </c>
@@ -2573,7 +2037,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
+    <row r="94" spans="1:2" ht="15">
       <c r="A94" s="2" t="s">
         <v>94</v>
       </c>
@@ -2581,7 +2045,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="95" spans="1:2">
+    <row r="95" spans="1:2" ht="15">
       <c r="A95" s="2" t="s">
         <v>95</v>
       </c>
@@ -2589,7 +2053,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:2">
+    <row r="96" spans="1:2" ht="15">
       <c r="A96" s="2" t="s">
         <v>96</v>
       </c>
@@ -2597,7 +2061,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="97" spans="1:2">
+    <row r="97" spans="1:2" ht="15">
       <c r="A97" s="2" t="s">
         <v>97</v>
       </c>
@@ -2605,7 +2069,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="98" spans="1:2">
+    <row r="98" spans="1:2" ht="15">
       <c r="A98" s="2" t="s">
         <v>98</v>
       </c>
@@ -2613,7 +2077,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="99" spans="1:2">
+    <row r="99" spans="1:2" ht="15">
       <c r="A99" s="2" t="s">
         <v>99</v>
       </c>
@@ -2621,7 +2085,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100" spans="1:2">
+    <row r="100" spans="1:2" ht="15">
       <c r="A100" s="2" t="s">
         <v>100</v>
       </c>
@@ -2629,7 +2093,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="1:2">
+    <row r="101" spans="1:2" ht="15">
       <c r="A101" s="2" t="s">
         <v>101</v>
       </c>
@@ -2637,7 +2101,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="102" spans="1:2">
+    <row r="102" spans="1:2" ht="15">
       <c r="A102" s="2" t="s">
         <v>102</v>
       </c>
@@ -2645,7 +2109,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="1:2">
+    <row r="103" spans="1:2" ht="15">
       <c r="A103" s="2" t="s">
         <v>103</v>
       </c>
@@ -2653,7 +2117,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="104" spans="1:2">
+    <row r="104" spans="1:2" ht="15">
       <c r="A104" s="2" t="s">
         <v>104</v>
       </c>
@@ -2661,7 +2125,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="105" spans="1:2">
+    <row r="105" spans="1:2" ht="15">
       <c r="A105" s="2" t="s">
         <v>105</v>
       </c>
@@ -2669,7 +2133,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="106" spans="1:2">
+    <row r="106" spans="1:2" ht="15">
       <c r="A106" s="2" t="s">
         <v>106</v>
       </c>
@@ -2677,7 +2141,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:2">
+    <row r="107" spans="1:2" ht="15">
       <c r="A107" s="2" t="s">
         <v>107</v>
       </c>
@@ -2685,7 +2149,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108" spans="1:2">
+    <row r="108" spans="1:2" ht="15">
       <c r="A108" s="2" t="s">
         <v>108</v>
       </c>
@@ -2693,7 +2157,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="109" spans="1:2">
+    <row r="109" spans="1:2" ht="15">
       <c r="A109" s="2" t="s">
         <v>109</v>
       </c>
@@ -2701,7 +2165,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="110" spans="1:2">
+    <row r="110" spans="1:2" ht="15">
       <c r="A110" s="2" t="s">
         <v>110</v>
       </c>
@@ -2709,7 +2173,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="111" spans="1:2">
+    <row r="111" spans="1:2" ht="15">
       <c r="A111" s="2" t="s">
         <v>111</v>
       </c>
@@ -2717,7 +2181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:2">
+    <row r="112" spans="1:2" ht="15">
       <c r="A112" s="2" t="s">
         <v>112</v>
       </c>
@@ -2725,7 +2189,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="113" spans="1:2">
+    <row r="113" spans="1:2" ht="15">
       <c r="A113" s="2" t="s">
         <v>113</v>
       </c>
@@ -2733,7 +2197,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="114" spans="1:2">
+    <row r="114" spans="1:2" ht="15">
       <c r="A114" s="2" t="s">
         <v>114</v>
       </c>
@@ -2741,7 +2205,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="115" spans="1:2">
+    <row r="115" spans="1:2" ht="15">
       <c r="A115" s="2" t="s">
         <v>115</v>
       </c>
@@ -2749,7 +2213,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="116" spans="1:2">
+    <row r="116" spans="1:2" ht="15">
       <c r="A116" s="2" t="s">
         <v>116</v>
       </c>
@@ -2757,7 +2221,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="117" spans="1:2">
+    <row r="117" spans="1:2" ht="15">
       <c r="A117" s="2" t="s">
         <v>117</v>
       </c>
@@ -2765,7 +2229,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="118" spans="1:2">
+    <row r="118" spans="1:2" ht="15">
       <c r="A118" s="2" t="s">
         <v>118</v>
       </c>
@@ -2773,7 +2237,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="119" spans="1:2">
+    <row r="119" spans="1:2" ht="15">
       <c r="A119" s="2" t="s">
         <v>119</v>
       </c>
@@ -2781,7 +2245,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="120" spans="1:2">
+    <row r="120" spans="1:2" ht="15">
       <c r="A120" s="2" t="s">
         <v>120</v>
       </c>
@@ -2789,7 +2253,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="121" spans="1:2">
+    <row r="121" spans="1:2" ht="15">
       <c r="A121" s="2" t="s">
         <v>121</v>
       </c>
@@ -2797,7 +2261,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="122" spans="1:2">
+    <row r="122" spans="1:2" ht="15">
       <c r="A122" s="2" t="s">
         <v>122</v>
       </c>
@@ -2805,7 +2269,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="123" spans="1:2">
+    <row r="123" spans="1:2" ht="15">
       <c r="A123" s="2" t="s">
         <v>123</v>
       </c>
@@ -2813,7 +2277,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="124" spans="1:2">
+    <row r="124" spans="1:2" ht="15">
       <c r="A124" s="2" t="s">
         <v>124</v>
       </c>
@@ -2821,7 +2285,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="125" spans="1:2">
+    <row r="125" spans="1:2" ht="15">
       <c r="A125" s="2" t="s">
         <v>125</v>
       </c>
@@ -2829,7 +2293,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="126" spans="1:2">
+    <row r="126" spans="1:2" ht="15">
       <c r="A126" s="2" t="s">
         <v>126</v>
       </c>
@@ -2837,7 +2301,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="127" spans="1:2">
+    <row r="127" spans="1:2" ht="15">
       <c r="A127" s="2" t="s">
         <v>127</v>
       </c>
@@ -2845,7 +2309,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="128" spans="1:2">
+    <row r="128" spans="1:2" ht="15">
       <c r="A128" s="2" t="s">
         <v>128</v>
       </c>
@@ -2853,7 +2317,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="129" spans="1:2">
+    <row r="129" spans="1:2" ht="15">
       <c r="A129" s="2" t="s">
         <v>129</v>
       </c>
@@ -2861,7 +2325,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="130" spans="1:2">
+    <row r="130" spans="1:2" ht="15">
       <c r="A130" s="2" t="s">
         <v>130</v>
       </c>
@@ -2869,7 +2333,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="131" spans="1:2">
+    <row r="131" spans="1:2" ht="15">
       <c r="A131" s="2" t="s">
         <v>131</v>
       </c>
@@ -2877,7 +2341,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="132" spans="1:2">
+    <row r="132" spans="1:2" ht="15">
       <c r="A132" s="2" t="s">
         <v>132</v>
       </c>
@@ -2885,7 +2349,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="133" spans="1:2">
+    <row r="133" spans="1:2" ht="15">
       <c r="A133" s="2" t="s">
         <v>133</v>
       </c>
@@ -2893,7 +2357,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="134" spans="1:2">
+    <row r="134" spans="1:2" ht="15">
       <c r="A134" s="2" t="s">
         <v>134</v>
       </c>
@@ -2901,7 +2365,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="135" spans="1:2">
+    <row r="135" spans="1:2" ht="15">
       <c r="A135" s="2" t="s">
         <v>135</v>
       </c>
@@ -2909,7 +2373,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:2">
+    <row r="136" spans="1:2" ht="15">
       <c r="A136" s="2" t="s">
         <v>136</v>
       </c>
@@ -2917,7 +2381,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="1:2">
+    <row r="137" spans="1:2" ht="15">
       <c r="A137" s="2" t="s">
         <v>137</v>
       </c>
@@ -2925,7 +2389,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="138" spans="1:2">
+    <row r="138" spans="1:2" ht="15">
       <c r="A138" s="2" t="s">
         <v>138</v>
       </c>
@@ -2933,7 +2397,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="139" spans="1:2">
+    <row r="139" spans="1:2" ht="15">
       <c r="A139" s="2" t="s">
         <v>139</v>
       </c>
@@ -2941,7 +2405,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="140" spans="1:2">
+    <row r="140" spans="1:2" ht="15">
       <c r="A140" s="2" t="s">
         <v>140</v>
       </c>
@@ -2949,7 +2413,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="141" spans="1:2">
+    <row r="141" spans="1:2" ht="15">
       <c r="A141" s="2" t="s">
         <v>141</v>
       </c>
@@ -2957,7 +2421,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="142" spans="1:2">
+    <row r="142" spans="1:2" ht="15">
       <c r="A142" s="2" t="s">
         <v>142</v>
       </c>
@@ -2965,7 +2429,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="143" spans="1:2">
+    <row r="143" spans="1:2" ht="15">
       <c r="A143" s="2" t="s">
         <v>143</v>
       </c>
@@ -2973,7 +2437,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="144" spans="1:2">
+    <row r="144" spans="1:2" ht="15">
       <c r="A144" s="2" t="s">
         <v>144</v>
       </c>
@@ -2981,7 +2445,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="145" spans="1:2">
+    <row r="145" spans="1:2" ht="15">
       <c r="A145" s="2" t="s">
         <v>145</v>
       </c>
@@ -2989,7 +2453,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="146" spans="1:2">
+    <row r="146" spans="1:2" ht="15">
       <c r="A146" s="2" t="s">
         <v>146</v>
       </c>
@@ -2997,7 +2461,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="147" spans="1:2">
+    <row r="147" spans="1:2" ht="15">
       <c r="A147" s="2" t="s">
         <v>147</v>
       </c>
@@ -3005,7 +2469,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="148" spans="1:2">
+    <row r="148" spans="1:2" ht="15">
       <c r="A148" s="2" t="s">
         <v>148</v>
       </c>
@@ -3013,7 +2477,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="149" spans="1:2">
+    <row r="149" spans="1:2" ht="15">
       <c r="A149" s="2" t="s">
         <v>149</v>
       </c>
@@ -3021,7 +2485,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="150" spans="1:2">
+    <row r="150" spans="1:2" ht="15">
       <c r="A150" s="2" t="s">
         <v>150</v>
       </c>
@@ -3029,7 +2493,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="151" spans="1:2">
+    <row r="151" spans="1:2" ht="15">
       <c r="A151" s="2" t="s">
         <v>151</v>
       </c>
@@ -3037,7 +2501,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="152" spans="1:2">
+    <row r="152" spans="1:2" ht="15">
       <c r="A152" s="2" t="s">
         <v>152</v>
       </c>
@@ -3045,7 +2509,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="153" spans="1:2">
+    <row r="153" spans="1:2" ht="15">
       <c r="A153" s="2" t="s">
         <v>153</v>
       </c>
@@ -3053,7 +2517,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="154" spans="1:2">
+    <row r="154" spans="1:2" ht="15">
       <c r="A154" s="2" t="s">
         <v>154</v>
       </c>
@@ -3061,7 +2525,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="155" spans="1:2">
+    <row r="155" spans="1:2" ht="15">
       <c r="A155" s="2" t="s">
         <v>155</v>
       </c>
@@ -3069,7 +2533,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="156" spans="1:2">
+    <row r="156" spans="1:2" ht="15">
       <c r="A156" s="2" t="s">
         <v>156</v>
       </c>
@@ -3077,7 +2541,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="157" spans="1:2">
+    <row r="157" spans="1:2" ht="15">
       <c r="A157" s="2" t="s">
         <v>157</v>
       </c>
@@ -3085,7 +2549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:2">
+    <row r="158" spans="1:2" ht="15">
       <c r="A158" s="2" t="s">
         <v>158</v>
       </c>
@@ -3093,7 +2557,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="159" spans="1:2">
+    <row r="159" spans="1:2" ht="15">
       <c r="A159" s="2" t="s">
         <v>159</v>
       </c>
@@ -3101,7 +2565,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="160" spans="1:2">
+    <row r="160" spans="1:2" ht="15">
       <c r="A160" s="2" t="s">
         <v>160</v>
       </c>
@@ -3109,7 +2573,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="161" spans="1:2">
+    <row r="161" spans="1:2" ht="15">
       <c r="A161" s="2" t="s">
         <v>161</v>
       </c>
@@ -3117,7 +2581,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="162" spans="1:2">
+    <row r="162" spans="1:2" ht="15">
       <c r="A162" s="2" t="s">
         <v>162</v>
       </c>
@@ -3125,7 +2589,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="163" spans="1:2">
+    <row r="163" spans="1:2" ht="15">
       <c r="A163" s="2" t="s">
         <v>163</v>
       </c>
@@ -3133,7 +2597,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="164" spans="1:2">
+    <row r="164" spans="1:2" ht="15">
       <c r="A164" s="2" t="s">
         <v>164</v>
       </c>
@@ -3141,7 +2605,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="165" spans="1:2">
+    <row r="165" spans="1:2" ht="15">
       <c r="A165" s="2" t="s">
         <v>165</v>
       </c>
@@ -3149,7 +2613,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="166" spans="1:2">
+    <row r="166" spans="1:2" ht="15">
       <c r="A166" s="2" t="s">
         <v>166</v>
       </c>
@@ -3157,7 +2621,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="167" spans="1:2">
+    <row r="167" spans="1:2" ht="15">
       <c r="A167" s="2" t="s">
         <v>167</v>
       </c>
@@ -3165,7 +2629,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="168" spans="1:2">
+    <row r="168" spans="1:2" ht="15">
       <c r="A168" s="2" t="s">
         <v>168</v>
       </c>
@@ -3173,7 +2637,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="169" spans="1:2">
+    <row r="169" spans="1:2" ht="15">
       <c r="A169" s="2" t="s">
         <v>169</v>
       </c>
@@ -3181,7 +2645,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="170" spans="1:2">
+    <row r="170" spans="1:2" ht="15">
       <c r="A170" s="2" t="s">
         <v>170</v>
       </c>
@@ -3189,7 +2653,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="171" spans="1:2">
+    <row r="171" spans="1:2" ht="15">
       <c r="A171" s="2" t="s">
         <v>171</v>
       </c>
@@ -3197,7 +2661,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="172" spans="1:2">
+    <row r="172" spans="1:2" ht="15">
       <c r="A172" s="2" t="s">
         <v>172</v>
       </c>
@@ -3205,7 +2669,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="173" spans="1:2">
+    <row r="173" spans="1:2" ht="15">
       <c r="A173" s="2" t="s">
         <v>173</v>
       </c>
@@ -3213,7 +2677,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="174" spans="1:2">
+    <row r="174" spans="1:2" ht="15">
       <c r="A174" s="2" t="s">
         <v>174</v>
       </c>
@@ -3221,7 +2685,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="175" spans="1:2">
+    <row r="175" spans="1:2" ht="15">
       <c r="A175" s="2" t="s">
         <v>175</v>
       </c>
@@ -3229,7 +2693,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="176" spans="1:2">
+    <row r="176" spans="1:2" ht="15">
       <c r="A176" s="2" t="s">
         <v>176</v>
       </c>
@@ -3237,7 +2701,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="177" spans="1:2">
+    <row r="177" spans="1:2" ht="15">
       <c r="A177" s="2" t="s">
         <v>177</v>
       </c>
@@ -3245,7 +2709,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="178" spans="1:2">
+    <row r="178" spans="1:2" ht="15">
       <c r="A178" s="2" t="s">
         <v>178</v>
       </c>
@@ -3253,7 +2717,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="179" spans="1:2">
+    <row r="179" spans="1:2" ht="15">
       <c r="A179" s="2" t="s">
         <v>179</v>
       </c>
@@ -3261,7 +2725,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="180" spans="1:2">
+    <row r="180" spans="1:2" ht="15">
       <c r="A180" s="2" t="s">
         <v>180</v>
       </c>
@@ -3269,7 +2733,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="181" spans="1:2">
+    <row r="181" spans="1:2" ht="15">
       <c r="A181" s="2" t="s">
         <v>181</v>
       </c>
@@ -3277,7 +2741,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="182" spans="1:2">
+    <row r="182" spans="1:2" ht="15">
       <c r="A182" s="2" t="s">
         <v>182</v>
       </c>
@@ -3285,7 +2749,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="183" spans="1:2">
+    <row r="183" spans="1:2" ht="15">
       <c r="A183" s="2" t="s">
         <v>183</v>
       </c>
@@ -3293,7 +2757,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="184" spans="1:2">
+    <row r="184" spans="1:2" ht="15">
       <c r="A184" s="2" t="s">
         <v>184</v>
       </c>
@@ -3301,7 +2765,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="185" spans="1:2">
+    <row r="185" spans="1:2" ht="15">
       <c r="A185" s="2" t="s">
         <v>185</v>
       </c>
@@ -3309,7 +2773,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="186" spans="1:2">
+    <row r="186" spans="1:2" ht="15">
       <c r="A186" s="2" t="s">
         <v>186</v>
       </c>
@@ -3317,7 +2781,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="187" spans="1:2">
+    <row r="187" spans="1:2" ht="15">
       <c r="A187" s="2" t="s">
         <v>187</v>
       </c>
@@ -3325,7 +2789,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="188" spans="1:2">
+    <row r="188" spans="1:2" ht="15">
       <c r="A188" s="2" t="s">
         <v>188</v>
       </c>
@@ -3333,7 +2797,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="189" spans="1:2">
+    <row r="189" spans="1:2" ht="15">
       <c r="A189" s="2" t="s">
         <v>189</v>
       </c>
@@ -3341,7 +2805,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="190" spans="1:2">
+    <row r="190" spans="1:2" ht="15">
       <c r="A190" s="2" t="s">
         <v>190</v>
       </c>
@@ -3349,7 +2813,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="191" spans="1:2">
+    <row r="191" spans="1:2" ht="15">
       <c r="A191" s="2" t="s">
         <v>191</v>
       </c>
@@ -3357,7 +2821,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="192" spans="1:2">
+    <row r="192" spans="1:2" ht="15">
       <c r="A192" s="2" t="s">
         <v>192</v>
       </c>
@@ -3365,7 +2829,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="193" spans="1:2">
+    <row r="193" spans="1:2" ht="15">
       <c r="A193" s="2" t="s">
         <v>193</v>
       </c>
@@ -3373,7 +2837,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="194" spans="1:2">
+    <row r="194" spans="1:2" ht="15">
       <c r="A194" s="2" t="s">
         <v>194</v>
       </c>
@@ -3381,7 +2845,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="195" spans="1:2">
+    <row r="195" spans="1:2" ht="15">
       <c r="A195" s="2" t="s">
         <v>195</v>
       </c>
@@ -3389,13 +2853,13 @@
         <v>50</v>
       </c>
     </row>
-    <row r="196" spans="1:2">
+    <row r="196" spans="1:2" ht="15">
       <c r="A196" s="2" t="s">
         <v>196</v>
       </c>
       <c r="B196" s="3"/>
     </row>
-    <row r="197" spans="1:2">
+    <row r="197" spans="1:2" ht="15">
       <c r="A197" s="2" t="s">
         <v>197</v>
       </c>
@@ -3403,7 +2867,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="198" spans="1:2">
+    <row r="198" spans="1:2" ht="15">
       <c r="A198" s="2" t="s">
         <v>198</v>
       </c>
@@ -3411,7 +2875,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="199" spans="1:2">
+    <row r="199" spans="1:2" ht="15">
       <c r="A199" s="2" t="s">
         <v>199</v>
       </c>
@@ -3419,7 +2883,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="200" spans="1:2">
+    <row r="200" spans="1:2" ht="15">
       <c r="A200" s="2" t="s">
         <v>200</v>
       </c>
@@ -3427,7 +2891,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="201" spans="1:2">
+    <row r="201" spans="1:2" ht="15">
       <c r="A201" s="2" t="s">
         <v>201</v>
       </c>
@@ -3435,7 +2899,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="202" spans="1:2">
+    <row r="202" spans="1:2" ht="15">
       <c r="A202" s="2" t="s">
         <v>202</v>
       </c>
@@ -3443,7 +2907,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="203" spans="1:2">
+    <row r="203" spans="1:2" ht="15">
       <c r="A203" s="2" t="s">
         <v>203</v>
       </c>
@@ -3451,7 +2915,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="204" spans="1:2">
+    <row r="204" spans="1:2" ht="15">
       <c r="A204" s="2" t="s">
         <v>204</v>
       </c>
@@ -3459,7 +2923,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="205" spans="1:2">
+    <row r="205" spans="1:2" ht="15">
       <c r="A205" s="2" t="s">
         <v>205</v>
       </c>
@@ -3467,7 +2931,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="206" spans="1:2">
+    <row r="206" spans="1:2" ht="15">
       <c r="A206" s="2" t="s">
         <v>206</v>
       </c>
@@ -3475,7 +2939,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="207" spans="1:2">
+    <row r="207" spans="1:2" ht="15">
       <c r="A207" s="2" t="s">
         <v>207</v>
       </c>
@@ -3483,7 +2947,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="208" spans="1:2">
+    <row r="208" spans="1:2" ht="15">
       <c r="A208" s="2" t="s">
         <v>208</v>
       </c>
@@ -3491,7 +2955,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="209" spans="1:2">
+    <row r="209" spans="1:2" ht="15">
       <c r="A209" s="2" t="s">
         <v>209</v>
       </c>
@@ -3499,7 +2963,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="210" spans="1:2">
+    <row r="210" spans="1:2" ht="15">
       <c r="A210" s="2" t="s">
         <v>210</v>
       </c>
@@ -3507,7 +2971,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="211" spans="1:2">
+    <row r="211" spans="1:2" ht="15">
       <c r="A211" s="2" t="s">
         <v>211</v>
       </c>
@@ -3515,7 +2979,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="212" spans="1:2">
+    <row r="212" spans="1:2" ht="15">
       <c r="A212" s="2" t="s">
         <v>212</v>
       </c>
@@ -3523,7 +2987,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="213" spans="1:2">
+    <row r="213" spans="1:2" ht="15">
       <c r="A213" s="2" t="s">
         <v>213</v>
       </c>
@@ -3531,7 +2995,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="214" spans="1:2">
+    <row r="214" spans="1:2" ht="15">
       <c r="A214" s="2" t="s">
         <v>214</v>
       </c>
@@ -3539,7 +3003,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="215" spans="1:2">
+    <row r="215" spans="1:2" ht="15">
       <c r="A215" s="2" t="s">
         <v>215</v>
       </c>
@@ -3547,7 +3011,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="216" spans="1:2">
+    <row r="216" spans="1:2" ht="15">
       <c r="A216" s="2" t="s">
         <v>216</v>
       </c>
@@ -3555,7 +3019,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="217" spans="1:2">
+    <row r="217" spans="1:2" ht="15">
       <c r="A217" s="2" t="s">
         <v>217</v>
       </c>
@@ -3563,7 +3027,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="218" spans="1:2">
+    <row r="218" spans="1:2" ht="15">
       <c r="A218" s="2" t="s">
         <v>218</v>
       </c>
@@ -3571,7 +3035,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="219" spans="1:2">
+    <row r="219" spans="1:2" ht="15">
       <c r="A219" s="2" t="s">
         <v>219</v>
       </c>
@@ -3579,7 +3043,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="220" spans="1:2">
+    <row r="220" spans="1:2" ht="15">
       <c r="A220" s="2" t="s">
         <v>220</v>
       </c>
@@ -3587,7 +3051,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="221" spans="1:2">
+    <row r="221" spans="1:2" ht="15">
       <c r="A221" s="2" t="s">
         <v>221</v>
       </c>
@@ -3595,7 +3059,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="222" spans="1:2">
+    <row r="222" spans="1:2" ht="15">
       <c r="A222" s="2" t="s">
         <v>222</v>
       </c>
@@ -3603,7 +3067,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="223" spans="1:2">
+    <row r="223" spans="1:2" ht="15">
       <c r="A223" s="2" t="s">
         <v>223</v>
       </c>
@@ -3611,7 +3075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:2">
+    <row r="224" spans="1:2" ht="15">
       <c r="A224" s="2" t="s">
         <v>224</v>
       </c>
@@ -3619,7 +3083,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="225" spans="1:2">
+    <row r="225" spans="1:2" ht="15">
       <c r="A225" s="2" t="s">
         <v>225</v>
       </c>
@@ -3627,7 +3091,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="226" spans="1:2">
+    <row r="226" spans="1:2" ht="15">
       <c r="A226" s="2" t="s">
         <v>226</v>
       </c>
@@ -3635,7 +3099,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="227" spans="1:2">
+    <row r="227" spans="1:2" ht="15">
       <c r="A227" s="2" t="s">
         <v>227</v>
       </c>
@@ -3643,7 +3107,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="228" spans="1:2">
+    <row r="228" spans="1:2" ht="15">
       <c r="A228" s="2" t="s">
         <v>228</v>
       </c>
@@ -3651,7 +3115,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="229" spans="1:2">
+    <row r="229" spans="1:2" ht="15">
       <c r="A229" s="2" t="s">
         <v>229</v>
       </c>
@@ -3659,7 +3123,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="230" spans="1:2">
+    <row r="230" spans="1:2" ht="15">
       <c r="A230" s="2" t="s">
         <v>230</v>
       </c>
@@ -3667,7 +3131,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="231" spans="1:2">
+    <row r="231" spans="1:2" ht="15">
       <c r="A231" s="2" t="s">
         <v>231</v>
       </c>
@@ -3675,7 +3139,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="232" spans="1:2">
+    <row r="232" spans="1:2" ht="15">
       <c r="A232" s="2" t="s">
         <v>232</v>
       </c>
@@ -3683,7 +3147,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="233" spans="1:2">
+    <row r="233" spans="1:2" ht="15">
       <c r="A233" s="2" t="s">
         <v>233</v>
       </c>
@@ -3691,7 +3155,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="234" spans="1:2">
+    <row r="234" spans="1:2" ht="15">
       <c r="A234" s="2" t="s">
         <v>234</v>
       </c>
@@ -3699,7 +3163,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="235" spans="1:2">
+    <row r="235" spans="1:2" ht="15">
       <c r="A235" s="2" t="s">
         <v>235</v>
       </c>
@@ -3707,7 +3171,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="236" spans="1:2">
+    <row r="236" spans="1:2" ht="15">
       <c r="A236" s="2" t="s">
         <v>236</v>
       </c>
@@ -3715,7 +3179,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="237" spans="1:2">
+    <row r="237" spans="1:2" ht="15">
       <c r="A237" s="2" t="s">
         <v>237</v>
       </c>
@@ -3723,7 +3187,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="238" spans="1:2">
+    <row r="238" spans="1:2" ht="15">
       <c r="A238" s="2" t="s">
         <v>238</v>
       </c>
@@ -3731,7 +3195,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="239" spans="1:2">
+    <row r="239" spans="1:2" ht="15">
       <c r="A239" s="2" t="s">
         <v>239</v>
       </c>
@@ -3739,7 +3203,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="240" spans="1:2">
+    <row r="240" spans="1:2" ht="15">
       <c r="A240" s="2" t="s">
         <v>240</v>
       </c>
@@ -3747,7 +3211,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="241" spans="1:2">
+    <row r="241" spans="1:2" ht="15">
       <c r="A241" s="2" t="s">
         <v>241</v>
       </c>
@@ -3755,13 +3219,13 @@
         <v>2</v>
       </c>
     </row>
-    <row r="242" spans="1:2">
+    <row r="242" spans="1:2" ht="15">
       <c r="A242" s="2" t="s">
         <v>242</v>
       </c>
       <c r="B242" s="3"/>
     </row>
-    <row r="243" spans="1:2">
+    <row r="243" spans="1:2" ht="15">
       <c r="A243" s="2" t="s">
         <v>243</v>
       </c>
@@ -3769,13 +3233,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:2">
+    <row r="244" spans="1:2" ht="15">
       <c r="A244" s="2" t="s">
         <v>244</v>
       </c>
       <c r="B244" s="3"/>
     </row>
-    <row r="245" spans="1:2">
+    <row r="245" spans="1:2" ht="15">
       <c r="A245" s="2" t="s">
         <v>245</v>
       </c>
@@ -3783,7 +3247,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="246" spans="1:2">
+    <row r="246" spans="1:2" ht="15">
       <c r="A246" s="2" t="s">
         <v>246</v>
       </c>
@@ -3791,7 +3255,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="247" spans="1:2">
+    <row r="247" spans="1:2" ht="15">
       <c r="A247" s="2" t="s">
         <v>247</v>
       </c>
@@ -3799,7 +3263,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="248" spans="1:2">
+    <row r="248" spans="1:2" ht="15">
       <c r="A248" s="2" t="s">
         <v>248</v>
       </c>
@@ -3807,13 +3271,13 @@
         <v>328</v>
       </c>
     </row>
-    <row r="249" spans="1:2">
+    <row r="249" spans="1:2" ht="15">
       <c r="A249" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B249" s="3"/>
     </row>
-    <row r="250" spans="1:2">
+    <row r="250" spans="1:2" ht="15">
       <c r="A250" s="2" t="s">
         <v>250</v>
       </c>
@@ -3821,7 +3285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:2">
+    <row r="251" spans="1:2" ht="15">
       <c r="A251" s="2" t="s">
         <v>251</v>
       </c>
@@ -3829,7 +3293,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="252" spans="1:2">
+    <row r="252" spans="1:2" ht="15">
       <c r="A252" s="2" t="s">
         <v>252</v>
       </c>
@@ -3837,7 +3301,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="253" spans="1:2">
+    <row r="253" spans="1:2" ht="15">
       <c r="A253" s="2" t="s">
         <v>253</v>
       </c>
@@ -3845,7 +3309,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="254" spans="1:2">
+    <row r="254" spans="1:2" ht="15">
       <c r="A254" s="2" t="s">
         <v>254</v>
       </c>
@@ -3853,7 +3317,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="255" spans="1:2">
+    <row r="255" spans="1:2" ht="15">
       <c r="A255" s="2" t="s">
         <v>255</v>
       </c>
@@ -3861,7 +3325,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="256" spans="1:2">
+    <row r="256" spans="1:2" ht="15">
       <c r="A256" s="2" t="s">
         <v>256</v>
       </c>
@@ -3869,7 +3333,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="257" spans="1:2">
+    <row r="257" spans="1:2" ht="15">
       <c r="A257" s="2" t="s">
         <v>257</v>
       </c>
@@ -3877,7 +3341,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="258" spans="1:2">
+    <row r="258" spans="1:2" ht="15">
       <c r="A258" s="2" t="s">
         <v>258</v>
       </c>
@@ -3885,7 +3349,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="259" spans="1:2">
+    <row r="259" spans="1:2" ht="15">
       <c r="A259" s="2" t="s">
         <v>259</v>
       </c>
@@ -3893,7 +3357,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="260" spans="1:2">
+    <row r="260" spans="1:2" ht="15">
       <c r="A260" s="2" t="s">
         <v>260</v>
       </c>
@@ -3901,7 +3365,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="261" spans="1:2">
+    <row r="261" spans="1:2" ht="15">
       <c r="A261" s="2" t="s">
         <v>261</v>
       </c>
@@ -3909,7 +3373,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="262" spans="1:2">
+    <row r="262" spans="1:2" ht="15">
       <c r="A262" s="2" t="s">
         <v>262</v>
       </c>
@@ -3917,7 +3381,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="263" spans="1:2">
+    <row r="263" spans="1:2" ht="15">
       <c r="A263" s="2" t="s">
         <v>263</v>
       </c>
@@ -3925,7 +3389,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="264" spans="1:2">
+    <row r="264" spans="1:2" ht="15">
       <c r="A264" s="2" t="s">
         <v>264</v>
       </c>
@@ -3933,7 +3397,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="265" spans="1:2">
+    <row r="265" spans="1:2" ht="15">
       <c r="A265" s="2" t="s">
         <v>265</v>
       </c>
@@ -3941,7 +3405,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="266" spans="1:2">
+    <row r="266" spans="1:2" ht="15">
       <c r="A266" s="2" t="s">
         <v>266</v>
       </c>
@@ -3949,7 +3413,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="267" spans="1:2">
+    <row r="267" spans="1:2" ht="15">
       <c r="A267" s="2" t="s">
         <v>267</v>
       </c>
@@ -3957,7 +3421,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="268" spans="1:2">
+    <row r="268" spans="1:2" ht="15">
       <c r="A268" s="2" t="s">
         <v>268</v>
       </c>
@@ -3965,7 +3429,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="269" spans="1:2">
+    <row r="269" spans="1:2" ht="15">
       <c r="A269" s="2" t="s">
         <v>269</v>
       </c>
@@ -3973,7 +3437,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="270" spans="1:2">
+    <row r="270" spans="1:2" ht="15">
       <c r="A270" s="2" t="s">
         <v>270</v>
       </c>
@@ -3981,7 +3445,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="271" spans="1:2">
+    <row r="271" spans="1:2" ht="15">
       <c r="A271" s="2" t="s">
         <v>271</v>
       </c>
@@ -3989,7 +3453,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="272" spans="1:2">
+    <row r="272" spans="1:2" ht="15">
       <c r="A272" s="2" t="s">
         <v>272</v>
       </c>
@@ -3997,7 +3461,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="273" spans="1:2">
+    <row r="273" spans="1:2" ht="15">
       <c r="A273" s="2" t="s">
         <v>273</v>
       </c>
@@ -4005,7 +3469,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="274" spans="1:2">
+    <row r="274" spans="1:2" ht="15">
       <c r="A274" s="2" t="s">
         <v>274</v>
       </c>
@@ -4013,7 +3477,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="275" spans="1:2">
+    <row r="275" spans="1:2" ht="15">
       <c r="A275" s="2" t="s">
         <v>275</v>
       </c>
@@ -4021,7 +3485,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="276" spans="1:2">
+    <row r="276" spans="1:2" ht="15">
       <c r="A276" s="2" t="s">
         <v>276</v>
       </c>
@@ -4029,7 +3493,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="277" spans="1:2">
+    <row r="277" spans="1:2" ht="15">
       <c r="A277" s="2" t="s">
         <v>277</v>
       </c>
@@ -4037,7 +3501,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="278" spans="1:2">
+    <row r="278" spans="1:2" ht="15">
       <c r="A278" s="2" t="s">
         <v>278</v>
       </c>
@@ -4045,7 +3509,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="279" spans="1:2">
+    <row r="279" spans="1:2" ht="15">
       <c r="A279" s="2" t="s">
         <v>279</v>
       </c>
@@ -4053,7 +3517,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="280" spans="1:2">
+    <row r="280" spans="1:2" ht="15">
       <c r="A280" s="2" t="s">
         <v>280</v>
       </c>
@@ -4061,7 +3525,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="281" spans="1:2">
+    <row r="281" spans="1:2" ht="15">
       <c r="A281" s="2" t="s">
         <v>281</v>
       </c>
@@ -4069,7 +3533,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="282" spans="1:2">
+    <row r="282" spans="1:2" ht="15">
       <c r="A282" s="2" t="s">
         <v>282</v>
       </c>
@@ -4077,7 +3541,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="283" spans="1:2">
+    <row r="283" spans="1:2" ht="15">
       <c r="A283" s="2" t="s">
         <v>283</v>
       </c>
@@ -4085,7 +3549,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="284" spans="1:2">
+    <row r="284" spans="1:2" ht="15">
       <c r="A284" s="2" t="s">
         <v>284</v>
       </c>
@@ -4093,7 +3557,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="285" spans="1:2">
+    <row r="285" spans="1:2" ht="15">
       <c r="A285" s="2" t="s">
         <v>285</v>
       </c>
@@ -4101,7 +3565,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="286" spans="1:2">
+    <row r="286" spans="1:2" ht="15">
       <c r="A286" s="2" t="s">
         <v>286</v>
       </c>
@@ -4109,7 +3573,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="287" spans="1:2">
+    <row r="287" spans="1:2" ht="15">
       <c r="A287" s="2" t="s">
         <v>287</v>
       </c>
@@ -4117,7 +3581,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="288" spans="1:2">
+    <row r="288" spans="1:2" ht="15">
       <c r="A288" s="2" t="s">
         <v>288</v>
       </c>
@@ -4125,7 +3589,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="289" spans="1:2">
+    <row r="289" spans="1:2" ht="15">
       <c r="A289" s="2" t="s">
         <v>289</v>
       </c>
@@ -4133,7 +3597,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="290" spans="1:2">
+    <row r="290" spans="1:2" ht="15">
       <c r="A290" s="2" t="s">
         <v>290</v>
       </c>
@@ -4141,7 +3605,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="291" spans="1:2">
+    <row r="291" spans="1:2" ht="15">
       <c r="A291" s="2" t="s">
         <v>291</v>
       </c>
@@ -4149,7 +3613,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="292" spans="1:2">
+    <row r="292" spans="1:2" ht="15">
       <c r="A292" s="2" t="s">
         <v>292</v>
       </c>
@@ -4157,7 +3621,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="293" spans="1:2">
+    <row r="293" spans="1:2" ht="15">
       <c r="A293" s="2" t="s">
         <v>293</v>
       </c>
@@ -4165,7 +3629,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="294" spans="1:2">
+    <row r="294" spans="1:2" ht="15">
       <c r="A294" s="2" t="s">
         <v>294</v>
       </c>
@@ -4173,7 +3637,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="295" spans="1:2">
+    <row r="295" spans="1:2" ht="15">
       <c r="A295" s="2" t="s">
         <v>295</v>
       </c>
@@ -4181,7 +3645,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="296" spans="1:2">
+    <row r="296" spans="1:2" ht="15">
       <c r="A296" s="2" t="s">
         <v>296</v>
       </c>
@@ -4189,7 +3653,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="297" spans="1:2">
+    <row r="297" spans="1:2" ht="15">
       <c r="A297" s="2" t="s">
         <v>297</v>
       </c>
@@ -4197,7 +3661,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="298" spans="1:2">
+    <row r="298" spans="1:2" ht="15">
       <c r="A298" s="2" t="s">
         <v>298</v>
       </c>
@@ -4205,13 +3669,13 @@
         <v>100</v>
       </c>
     </row>
-    <row r="299" spans="1:2">
+    <row r="299" spans="1:2" ht="15">
       <c r="A299" s="2" t="s">
         <v>299</v>
       </c>
       <c r="B299" s="3"/>
     </row>
-    <row r="300" spans="1:2">
+    <row r="300" spans="1:2" ht="15">
       <c r="A300" s="2" t="s">
         <v>300</v>
       </c>
@@ -4221,6 +3685,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>